--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260911.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260911.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>15.37%</t>
+          <t>15.45%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>6.68%</t>
+          <t>6.63%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.31%</t>
+          <t>6.28%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.51%</t>
+          <t>5.62%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.38%</t>
+          <t>5.41%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.02%</t>
+          <t>5.06%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.13%</t>
+          <t>4.21%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.96%</t>
+          <t>4.04%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.91%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.85%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.85%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.61%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.87%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
@@ -997,176 +997,176 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,800,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2,800,000</t>
+          <t>1,293,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>1,293,000</t>
+          <t>120,500</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>120,500</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>1,580,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,580,000</t>
+          <t>760,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>760,000</t>
+          <t>5,360,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>5,360,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1276,24 +1276,24 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>1,100,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,100,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>700,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
@@ -1547,39 +1547,39 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>7,010,382,185</t>
+          <t>8,164,494,045</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>2,579,837,073</t>
+          <t>2,395,349,174</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>3,474,325,080</t>
+          <t>3,048,350,129</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
